--- a/BVSimulationFiles/80.xlsx
+++ b/BVSimulationFiles/80.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001610017889087657</v>
+        <v>0.003220035778175314</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00160807098635543</v>
+        <v>0.00321614197271086</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001606126437901547</v>
+        <v>0.003212252875803094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001604184240879112</v>
+        <v>0.003208368481758224</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001602244392444675</v>
+        <v>0.00320448878488935</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001600306889758221</v>
+        <v>0.003200613779516442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001598371729983172</v>
+        <v>0.003196743459966344</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001596438910286379</v>
+        <v>0.003192877820572758</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001594508427838118</v>
+        <v>0.003189016855676236</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001592580279812088</v>
+        <v>0.003185160559624176</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001590654463385406</v>
+        <v>0.003181308926770812</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001588730975738602</v>
+        <v>0.003177461951477204</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001586809814055615</v>
+        <v>0.00317361962811123</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00158489097552379</v>
+        <v>0.00316978195104758</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001582974457333872</v>
+        <v>0.003165948914667744</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001581060256680005</v>
+        <v>0.00316212051336001</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001579148370759725</v>
+        <v>0.00315829674151945</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001577238796773957</v>
+        <v>0.003154477593547914</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00157533153192701</v>
+        <v>0.00315066306385402</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001573426573426574</v>
+        <v>0.003146853146853148</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001610017889087657</v>
+        <v>0.003220035778175314</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00160807098635543</v>
+        <v>0.00321614197271086</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001606126437901547</v>
+        <v>0.003212252875803094</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001604184240879112</v>
+        <v>0.003208368481758224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001602244392444675</v>
+        <v>0.00320448878488935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001600306889758221</v>
+        <v>0.003200613779516442</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001598371729983172</v>
+        <v>0.003196743459966344</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001596438910286379</v>
+        <v>0.003192877820572758</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001594508427838118</v>
+        <v>0.003189016855676236</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001592580279812088</v>
+        <v>0.003185160559624176</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001590654463385406</v>
+        <v>0.003181308926770812</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001588730975738602</v>
+        <v>0.003177461951477204</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001586809814055615</v>
+        <v>0.00317361962811123</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00158489097552379</v>
+        <v>0.00316978195104758</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001582974457333872</v>
+        <v>0.003165948914667744</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001581060256680005</v>
+        <v>0.00316212051336001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001579148370759725</v>
+        <v>0.00315829674151945</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001577238796773957</v>
+        <v>0.003154477593547914</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00157533153192701</v>
+        <v>0.00315066306385402</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001573426573426574</v>
+        <v>0.003146853146853148</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/80.xlsx
+++ b/BVSimulationFiles/80.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003220035778175314</v>
+        <v>0.03220035778175314</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00321614197271086</v>
+        <v>0.0321614197271086</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003212252875803094</v>
+        <v>0.03212252875803094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003208368481758224</v>
+        <v>0.03208368481758224</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00320448878488935</v>
+        <v>0.0320448878488935</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003200613779516442</v>
+        <v>0.03200613779516442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003196743459966344</v>
+        <v>0.03196743459966344</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003192877820572758</v>
+        <v>0.03192877820572758</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003189016855676236</v>
+        <v>0.03189016855676235</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003185160559624176</v>
+        <v>0.03185160559624176</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003181308926770812</v>
+        <v>0.03181308926770812</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003177461951477204</v>
+        <v>0.03177461951477203</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00317361962811123</v>
+        <v>0.0317361962811123</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00316978195104758</v>
+        <v>0.0316978195104758</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003165948914667744</v>
+        <v>0.03165948914667744</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00316212051336001</v>
+        <v>0.0316212051336001</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00315829674151945</v>
+        <v>0.0315829674151945</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003154477593547914</v>
+        <v>0.03154477593547914</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00315066306385402</v>
+        <v>0.0315066306385402</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003146853146853148</v>
+        <v>0.03146853146853148</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.003220035778175314</v>
+        <v>0.03220035778175314</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00321614197271086</v>
+        <v>0.0321614197271086</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003212252875803094</v>
+        <v>0.03212252875803094</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003208368481758224</v>
+        <v>0.03208368481758224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00320448878488935</v>
+        <v>0.0320448878488935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003200613779516442</v>
+        <v>0.03200613779516442</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003196743459966344</v>
+        <v>0.03196743459966344</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003192877820572758</v>
+        <v>0.03192877820572758</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003189016855676236</v>
+        <v>0.03189016855676235</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003185160559624176</v>
+        <v>0.03185160559624176</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003181308926770812</v>
+        <v>0.03181308926770812</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003177461951477204</v>
+        <v>0.03177461951477203</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00317361962811123</v>
+        <v>0.0317361962811123</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00316978195104758</v>
+        <v>0.0316978195104758</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003165948914667744</v>
+        <v>0.03165948914667744</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00316212051336001</v>
+        <v>0.0316212051336001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00315829674151945</v>
+        <v>0.0315829674151945</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003154477593547914</v>
+        <v>0.03154477593547914</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00315066306385402</v>
+        <v>0.0315066306385402</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003146853146853148</v>
+        <v>0.03146853146853148</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/80.xlsx
+++ b/BVSimulationFiles/80.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.002221052631578947</v>
+        <v>0.001455172413793103</v>
       </c>
       <c r="D1" t="n">
-        <v>0.004442105263157895</v>
+        <v>0.002910344827586207</v>
       </c>
       <c r="E1" t="n">
-        <v>0.006663157894736842</v>
+        <v>0.00436551724137931</v>
       </c>
       <c r="F1" t="n">
-        <v>0.00888421052631579</v>
+        <v>0.005820689655172413</v>
       </c>
       <c r="G1" t="n">
-        <v>0.01110526315789474</v>
+        <v>0.007275862068965517</v>
       </c>
       <c r="H1" t="n">
-        <v>0.01332631578947368</v>
+        <v>0.00873103448275862</v>
       </c>
       <c r="I1" t="n">
-        <v>0.01554736842105263</v>
+        <v>0.01018620689655172</v>
       </c>
       <c r="J1" t="n">
-        <v>0.01776842105263158</v>
+        <v>0.01164137931034483</v>
       </c>
       <c r="K1" t="n">
-        <v>0.01998947368421053</v>
+        <v>0.01309655172413793</v>
       </c>
       <c r="L1" t="n">
-        <v>0.02221052631578947</v>
+        <v>0.01455172413793103</v>
       </c>
       <c r="M1" t="n">
-        <v>0.02443157894736842</v>
+        <v>0.01600689655172414</v>
       </c>
       <c r="N1" t="n">
-        <v>0.02665263157894737</v>
+        <v>0.01746206896551724</v>
       </c>
       <c r="O1" t="n">
-        <v>0.02887368421052632</v>
+        <v>0.01891724137931034</v>
       </c>
       <c r="P1" t="n">
-        <v>0.03109473684210526</v>
+        <v>0.02037241379310345</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.03331578947368421</v>
+        <v>0.02182758620689655</v>
       </c>
       <c r="R1" t="n">
-        <v>0.03553684210526316</v>
+        <v>0.02328275862068965</v>
       </c>
       <c r="S1" t="n">
-        <v>0.0377578947368421</v>
+        <v>0.02473793103448275</v>
       </c>
       <c r="T1" t="n">
-        <v>0.03997894736842105</v>
+        <v>0.02619310344827586</v>
       </c>
       <c r="U1" t="n">
+        <v>0.02764827586206896</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.02910344827586207</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.03055862068965517</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.03201379310344828</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.03346896551724138</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.03492413793103448</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.03637931034482758</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.03783448275862068</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.03928965517241379</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.04074482758620689</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.04219999999999999</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03220035778175314</v>
+        <v>0.09167882129326635</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0321614197271086</v>
+        <v>0.09153358115592931</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03212252875803094</v>
+        <v>0.09138857111205544</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03208368481758224</v>
+        <v>0.09124379079712437</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0320448878488935</v>
+        <v>0.09109923984719302</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03200613779516442</v>
+        <v>0.09095491789889497</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03196743459966344</v>
+        <v>0.09081082458943962</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03192877820572758</v>
+        <v>0.09066695955661079</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03189016855676235</v>
+        <v>0.09052332243876643</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03185160559624176</v>
+        <v>0.09037991287483724</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03181308926770812</v>
+        <v>0.09023673050432589</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03177461951477203</v>
+        <v>0.09009377496730635</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0317361962811123</v>
+        <v>0.08995104590442272</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0316978195104758</v>
+        <v>0.08980854295688831</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03165948914667744</v>
+        <v>0.08966626576648495</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0316212051336001</v>
+        <v>0.08952421397556189</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0315829674151945</v>
+        <v>0.08938238722703497</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03154477593547914</v>
+        <v>0.0892407851643858</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0315066306385402</v>
+        <v>0.08909940743166084</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03146853146853148</v>
+        <v>0.08895825367347027</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0888173235349875</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.08867661666194791</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.08853613270064818</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.08839587129794534</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.08825583210125591</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.08811601475855499</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.08797641891837517</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.08783704422980611</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.08769789034249326</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08755895690663715</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03220035778175314</v>
+        <v>0.09167882129326635</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0321614197271086</v>
+        <v>0.09153358115592931</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03212252875803094</v>
+        <v>0.09138857111205544</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03208368481758224</v>
+        <v>0.09124379079712437</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0320448878488935</v>
+        <v>0.09109923984719302</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03200613779516442</v>
+        <v>0.09095491789889497</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03196743459966344</v>
+        <v>0.09081082458943962</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03192877820572758</v>
+        <v>0.09066695955661079</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03189016855676235</v>
+        <v>0.09052332243876643</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03185160559624176</v>
+        <v>0.09037991287483724</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03181308926770812</v>
+        <v>0.09023673050432589</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03177461951477203</v>
+        <v>0.09009377496730635</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0317361962811123</v>
+        <v>0.08995104590442272</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0316978195104758</v>
+        <v>0.08980854295688831</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03165948914667744</v>
+        <v>0.08966626576648495</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0316212051336001</v>
+        <v>0.08952421397556189</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0315829674151945</v>
+        <v>0.08938238722703497</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03154477593547914</v>
+        <v>0.0892407851643858</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0315066306385402</v>
+        <v>0.08909940743166084</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03146853146853148</v>
+        <v>0.08895825367347027</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.0888173235349875</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.08867661666194791</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.08853613270064818</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.08839587129794534</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.08825583210125591</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.08811601475855499</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.08797641891837517</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.08783704422980611</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.08769789034249326</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.08755895690663715</v>
       </c>
     </row>
   </sheetData>
